--- a/public/管理口径原因分析默认模版/常州项目部.xlsx
+++ b/public/管理口径原因分析默认模版/常州项目部.xlsx
@@ -4,23 +4,23 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" firstSheet="1" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
     <sheet sheetId="3" name="合计" state="visible" r:id="rId5"/>
     <sheet sheetId="4" name="常州酒店" state="visible" r:id="rId6"/>
     <sheet sheetId="5" name="江苏常州酒店能源转售" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="浙江湖州销售分公司配餐业务（停）" state="visible" r:id="rId8"/>
-    <sheet sheetId="7" name="江苏常州销售分公司配餐项目" state="visible" r:id="rId9"/>
-    <sheet sheetId="8" name="常州酒店项目部销售费用" state="visible" r:id="rId10"/>
+    <sheet sheetId="6" name="江苏常州销售分公司配餐项目" state="visible" r:id="rId8"/>
+    <sheet sheetId="7" name="常州酒店项目部销售费用" state="visible" r:id="rId9"/>
+    <sheet sheetId="8" name="南京中石油三江口汇能码头物业项目" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="109">
   <si>
     <t>工作表目录</t>
   </si>
@@ -43,16 +43,19 @@
     <t>江苏常州酒店能源转售</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务（停）</t>
-  </si>
-  <si>
     <t>江苏常州销售分公司配餐项目</t>
   </si>
   <si>
     <t>常州酒店项目部销售费用</t>
   </si>
   <si>
-    <t>合计预算执行分析（2026年06月）</t>
+    <t>南京中石油三江口汇能码头物业项目</t>
+  </si>
+  <si>
+    <t>非考核口径</t>
+  </si>
+  <si>
+    <t>合计预算执行分析（2026年07月）</t>
   </si>
   <si>
     <t>项目</t>
@@ -229,13 +232,13 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>常州酒店预算执行分析（2026年06月）</t>
-  </si>
-  <si>
-    <t>酒店自2025年2月26日自营，其中存在2个月的停业影响。收入增加157万元，客房收入增加45万元，租赁收入增加112万元，租赁收入增加为桔子和影音酒店的合作经营加入影响。</t>
-  </si>
-  <si>
-    <t>客房收入减少85万元，主要是团队收入远低于预算；餐饮收入减少112万元，早餐、团队餐、零点餐收入均低于预算；租赁收入减少25万元，其他收入减少6万元</t>
+    <t>常州酒店预算执行分析（2026年07月）</t>
+  </si>
+  <si>
+    <t>酒店自2025年2月26日自营，其中存在2个月的停业影响。收入增加153万元，客房收入增加45万元，租赁收入增加112万元，租赁收入增加为桔子和影音酒店的合作经营加入影响。</t>
+  </si>
+  <si>
+    <t>客房收入减少97万元，主要是团队收入远低于预算；餐饮收入减少109万元，早餐、团队餐、零点餐收入均低于预算；租赁收入减少37万元，其他收入减少5万元</t>
   </si>
   <si>
     <t>比上年同期减少餐饮食材采购</t>
@@ -244,16 +247,16 @@
     <t>减少食品的消耗</t>
   </si>
   <si>
-    <t>主要增加的是客用品消耗</t>
+    <t>比上年同期减少客用品消耗</t>
   </si>
   <si>
     <t>客房收入缺口大，消耗品也少于预期</t>
   </si>
   <si>
-    <t>比上年同期减少低值易耗品</t>
-  </si>
-  <si>
-    <t>增加的主要是床垫、防毒面罩、应急手电等低值易耗品</t>
+    <t>比上年同期减少商品成本</t>
+  </si>
+  <si>
+    <t>增加的主要是床垫、防毒面罩、应急手电等低值易耗品及销售商品成本</t>
   </si>
   <si>
     <t>上年同期1-2月未经营，且本年度气温较往年较低，空调开启时段加长，用气量增加</t>
@@ -283,19 +286,16 @@
     <t>合同化减少1人</t>
   </si>
   <si>
-    <t>其中上年同期劳务派遣转为外包人工，且今年同期含餐饮业务外包40万元，增加销售外包人员共计14万元</t>
+    <t>其中上年同期劳务派遣转为外包人工，较同期增加餐饮业务外包费用累计40万元，增加销售外包人员共计16万元</t>
   </si>
   <si>
     <t>其中主要是餐饮收入减少带来的餐饮业务外包费用减少</t>
   </si>
   <si>
-    <t>增加隐患类整改7万元，大堂、二楼装饰改造工程10.89万元。</t>
-  </si>
-  <si>
-    <t>增加隐患类整改7万元，</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上年同期1-2月未经营而增加的洗涤费用 </t>
+    <t>增加隐患类整改14万元，大堂、二楼装饰改造工程10.89万元</t>
+  </si>
+  <si>
+    <t>增加隐患类整改14万元，</t>
   </si>
   <si>
     <t>客房出租率减少，布草洗涤量减少；适当降低团队布草更换频率及布草配置以下降洗涤费用</t>
@@ -304,9 +304,6 @@
     <t>增加四害消杀0.58万元，二次水箱清洗0.69万元</t>
   </si>
   <si>
-    <t>减少预计的绿植养护费用</t>
-  </si>
-  <si>
     <t>办公费及差旅费均有所减少</t>
   </si>
   <si>
@@ -325,12 +322,15 @@
     <t>减少为上年6月暂估的餐饮费用24万元</t>
   </si>
   <si>
-    <t>减少财产保险4万元，审计费1.6万元，销售推广费6.6</t>
+    <t>减少财产保险4万元，审计费1.6万元，销售推广费7.7</t>
   </si>
   <si>
     <t>随应收账款余额的下降而下降</t>
   </si>
   <si>
+    <t>随应收账款余额的上升而上升，需加速应收账款回收</t>
+  </si>
+  <si>
     <t>随收入增加而增加各平台手续费</t>
   </si>
   <si>
@@ -343,7 +343,7 @@
     <t>招录贫困地区人员享受的增值税减免政策4月截止</t>
   </si>
   <si>
-    <t>江苏常州酒店能源转售预算执行分析（2026年06月）</t>
+    <t>江苏常州酒店能源转售预算执行分析（2026年07月）</t>
   </si>
   <si>
     <t>能源转售收入为桔子和影音酒店的合作经营加入影响。</t>
@@ -355,13 +355,19 @@
     <t>随收入的增加，能耗也相应增加</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务（停）预算执行分析（2026年06月）</t>
-  </si>
-  <si>
-    <t>江苏常州销售分公司配餐项目预算执行分析（2026年06月）</t>
-  </si>
-  <si>
-    <t>常州酒店项目部销售费用预算执行分析（2026年06月）</t>
+    <t>江苏常州销售分公司配餐项目预算执行分析（2026年07月）</t>
+  </si>
+  <si>
+    <t>常州酒店项目部销售费用预算执行分析（2026年07月）</t>
+  </si>
+  <si>
+    <t>南京中石油三江口汇能码头物业项目预算执行分析（2026年07月）</t>
+  </si>
+  <si>
+    <t>新增项目</t>
+  </si>
+  <si>
+    <t>新增项目，随收入增加对应成本增加</t>
   </si>
 </sst>
 </file>
@@ -866,8 +872,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="2" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -928,7 +934,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="5" t="str">
-        <f>HYPERLINK("#'浙江湖州销售分公司配餐业务（停）'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'江苏常州销售分公司配餐项目'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -938,18 +944,21 @@
         <v>8</v>
       </c>
       <c r="C7" s="5" t="str">
-        <f>HYPERLINK("#'江苏常州销售分公司配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'常州酒店项目部销售费用'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="5" t="str">
-        <f>HYPERLINK("#'常州酒店项目部销售费用'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'南京中石油三江口汇能码头物业项目'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -964,7 +973,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultRowHeight="17.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="53" style="6" customWidth="1"/>
     <col min="2" max="6" width="15" customWidth="1"/>
@@ -976,7 +985,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -994,51 +1003,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -1056,7 +1065,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1074,7 +1083,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1092,7 +1101,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1110,7 +1119,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1128,7 +1137,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1146,7 +1155,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -1164,7 +1173,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1182,7 +1191,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -1200,7 +1209,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1218,7 +1227,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1236,7 +1245,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -1254,7 +1263,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -1272,7 +1281,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -1290,7 +1299,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -1308,7 +1317,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1326,7 +1335,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1344,7 +1353,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -1362,7 +1371,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1380,7 +1389,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1398,7 +1407,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -1416,7 +1425,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -1434,7 +1443,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -1452,7 +1461,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -1470,7 +1479,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -1488,7 +1497,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -1506,7 +1515,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -1524,7 +1533,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -1542,7 +1551,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -1560,7 +1569,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1578,7 +1587,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -1596,7 +1605,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -1614,7 +1623,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -1632,7 +1641,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -1650,7 +1659,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -1668,7 +1677,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -1686,7 +1695,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -1704,7 +1713,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -1729,19 +1738,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultRowHeight="17.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="53" style="6" customWidth="1"/>
     <col min="2" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="38.2222222222222" customWidth="1"/>
+    <col min="7" max="7" width="39.375" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="37.3333333333333" customWidth="1"/>
+    <col min="9" max="9" width="31.25" customWidth="1"/>
     <col min="10" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1759,51 +1768,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" ht="104.4" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="112.5" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -1811,11 +1820,11 @@
       <c r="E3" s="24"/>
       <c r="F3" s="24"/>
       <c r="G3" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H3" s="24"/>
       <c r="I3" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J3" s="24"/>
       <c r="K3" s="24"/>
@@ -1825,7 +1834,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1843,7 +1852,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1861,7 +1870,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1869,11 +1878,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -1881,9 +1890,9 @@
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
     </row>
-    <row r="7" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1891,11 +1900,11 @@
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
@@ -1905,7 +1914,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1921,9 +1930,9 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -1931,11 +1940,11 @@
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
@@ -1943,53 +1952,53 @@
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" ht="52.2" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="56.25" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+        <v>32</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="11"/>
+        <v>72</v>
+      </c>
+      <c r="H10" s="24"/>
       <c r="I10" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-    </row>
-    <row r="11" ht="52.2" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+    </row>
+    <row r="11" ht="56.25" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+        <v>33</v>
+      </c>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
       <c r="G11" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="H11" s="11"/>
+        <v>74</v>
+      </c>
+      <c r="H11" s="24"/>
       <c r="I11" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
+        <v>75</v>
+      </c>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -2007,7 +2016,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -2025,7 +2034,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2033,11 +2042,11 @@
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
@@ -2045,9 +2054,9 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -2055,11 +2064,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -2069,7 +2078,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -2085,9 +2094,9 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -2095,11 +2104,11 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -2107,53 +2116,53 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" ht="69.6" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="75" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
       <c r="G18" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="11"/>
+        <v>81</v>
+      </c>
+      <c r="H18" s="24"/>
       <c r="I18" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-    </row>
-    <row r="19" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+    </row>
+    <row r="19" ht="37.5" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+        <v>41</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
       <c r="G19" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="11"/>
+        <v>83</v>
+      </c>
+      <c r="H19" s="24"/>
       <c r="I19" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
+        <v>84</v>
+      </c>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2169,53 +2178,49 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
     </row>
-    <row r="21" ht="52.2" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" ht="75" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="11"/>
+        <v>43</v>
+      </c>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="24"/>
       <c r="I21" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-    </row>
-    <row r="22" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+    </row>
+    <row r="22" ht="37.5" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
+        <v>44</v>
+      </c>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
       <c r="G22" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-    </row>
-    <row r="23" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H22" s="24"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2223,11 +2228,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -2235,9 +2240,9 @@
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
     </row>
-    <row r="24" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2245,11 +2250,11 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -2257,9 +2262,9 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
     </row>
-    <row r="25" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -2267,11 +2272,11 @@
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -2279,9 +2284,9 @@
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
     </row>
-    <row r="26" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2289,11 +2294,11 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -2303,7 +2308,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2319,9 +2324,9 @@
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2329,7 +2334,7 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="12" t="s">
@@ -2343,7 +2348,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -2359,9 +2364,9 @@
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
     </row>
-    <row r="30" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -2383,7 +2388,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -2401,7 +2406,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -2419,7 +2424,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -2437,7 +2442,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -2459,7 +2464,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -2475,9 +2480,9 @@
       <c r="M35" s="11"/>
       <c r="N35" s="11"/>
     </row>
-    <row r="36" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -2499,7 +2504,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -2517,7 +2522,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -2535,7 +2540,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -2553,7 +2558,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -2578,12 +2583,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultRowHeight="17.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="53" style="6" customWidth="1"/>
     <col min="2" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="32.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="19.5555555555556" customWidth="1"/>
+    <col min="7" max="7" width="24.3333333333333" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="24.3333333333333" customWidth="1"/>
     <col min="10" max="14" width="15" customWidth="1"/>
   </cols>
@@ -2608,51 +2613,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -2674,7 +2679,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -2692,7 +2697,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -2710,7 +2715,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -2728,7 +2733,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -2746,7 +2751,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -2764,7 +2769,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -2782,7 +2787,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -2798,9 +2803,9 @@
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
     </row>
-    <row r="11" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -2822,7 +2827,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -2840,7 +2845,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -2858,7 +2863,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2876,7 +2881,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -2894,7 +2899,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -2912,7 +2917,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -2930,7 +2935,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -2948,7 +2953,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -2966,7 +2971,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2984,7 +2989,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3002,7 +3007,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3020,7 +3025,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3038,7 +3043,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3056,7 +3061,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -3074,7 +3079,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3092,7 +3097,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3110,7 +3115,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3128,7 +3133,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3146,7 +3151,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3164,7 +3169,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3182,7 +3187,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3200,7 +3205,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3218,7 +3223,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -3236,7 +3241,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -3254,7 +3259,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -3272,7 +3277,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3290,7 +3295,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -3308,7 +3313,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -3326,7 +3331,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -3351,7 +3356,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultRowHeight="17.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="53" style="6" customWidth="1"/>
     <col min="2" max="6" width="15" customWidth="1"/>
@@ -3381,51 +3386,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -3443,7 +3448,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -3461,7 +3466,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -3479,7 +3484,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -3497,7 +3502,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -3515,7 +3520,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -3533,7 +3538,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -3551,7 +3556,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -3569,7 +3574,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -3587,7 +3592,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -3605,7 +3610,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -3623,7 +3628,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -3641,7 +3646,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3659,7 +3664,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3675,9 +3680,778 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
+    <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+    </row>
+    <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N40"/>
+  <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="53" style="6" customWidth="1"/>
+    <col min="2" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="24.3333333333333" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="24.3333333333333" customWidth="1"/>
+    <col min="10" max="14" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+    </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3695,7 +4469,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3713,7 +4487,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -3731,7 +4505,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -3749,7 +4523,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3767,7 +4541,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3785,7 +4559,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3803,7 +4577,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3821,7 +4595,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -3839,7 +4613,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3857,7 +4631,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3875,7 +4649,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3893,7 +4667,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3911,7 +4685,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3929,7 +4703,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3947,7 +4721,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3965,7 +4739,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3983,7 +4757,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -4001,7 +4775,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -4019,7 +4793,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4037,7 +4811,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4055,7 +4829,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -4073,7 +4847,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -4091,7 +4865,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4113,10 +4887,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultRowHeight="17.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="53" style="6" customWidth="1"/>
     <col min="2" max="6" width="15" customWidth="1"/>
@@ -4128,7 +4902,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4146,58 +4920,60 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>107</v>
+      </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
       <c r="J3" s="11"/>
@@ -4208,7 +4984,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -4226,7 +5002,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -4244,7 +5020,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -4262,7 +5038,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -4280,7 +5056,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -4298,7 +5074,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -4316,7 +5092,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -4334,7 +5110,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -4352,7 +5128,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -4370,7 +5146,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -4388,7 +5164,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -4406,7 +5182,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -4424,7 +5200,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -4440,18 +5216,16 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
-        <v>78</v>
-      </c>
+      <c r="G17" s="12"/>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
       <c r="J17" s="11"/>
@@ -4460,9 +5234,9 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" ht="34.8" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4470,7 +5244,7 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
@@ -4482,7 +5256,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4500,7 +5274,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4518,7 +5292,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4536,7 +5310,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -4554,7 +5328,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -4572,7 +5346,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -4590,7 +5364,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -4608,7 +5382,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -4626,7 +5400,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -4644,7 +5418,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -4662,7 +5436,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -4680,7 +5454,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -4698,7 +5472,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -4716,7 +5490,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -4734,7 +5508,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -4752,7 +5526,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -4770,7 +5544,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -4788,7 +5562,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4806,7 +5580,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4824,7 +5598,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -4842,7 +5616,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -4860,7 +5634,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4880,769 +5654,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultRowHeight="17.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="53" style="6" customWidth="1"/>
-    <col min="2" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="24.3333333333333" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="24.3333333333333" customWidth="1"/>
-    <col min="10" max="14" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
 </file>
--- a/public/管理口径原因分析默认模版/常州项目部.xlsx
+++ b/public/管理口径原因分析默认模版/常州项目部.xlsx
@@ -13,14 +13,13 @@
     <sheet sheetId="5" name="江苏常州酒店能源转售" state="visible" r:id="rId7"/>
     <sheet sheetId="6" name="江苏常州销售分公司配餐项目" state="visible" r:id="rId8"/>
     <sheet sheetId="7" name="常州酒店项目部销售费用" state="visible" r:id="rId9"/>
-    <sheet sheetId="8" name="南京中石油三江口汇能码头物业项目" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="110">
   <si>
     <t>工作表目录</t>
   </si>
@@ -47,12 +46,6 @@
   </si>
   <si>
     <t>常州酒店项目部销售费用</t>
-  </si>
-  <si>
-    <t>南京中石油三江口汇能码头物业项目</t>
-  </si>
-  <si>
-    <t>非考核口径</t>
   </si>
   <si>
     <t>合计预算执行分析（2026年07月）</t>
@@ -104,6 +97,12 @@
     <t>一、 营业收入</t>
   </si>
   <si>
+    <t>酒店自2025年2月26日自营，其中存在2个月的停业影响。酒店收入增加153万元，能源转售收入增加77万元。</t>
+  </si>
+  <si>
+    <t>客房收入减少97万元，主要是团队收入远低于预算；餐饮收入减少109万元，早餐、团队餐、零点餐收入均低于预算；租赁收入减少37万元，其他收入减少5万元</t>
+  </si>
+  <si>
     <t xml:space="preserve">     减:（一）经营性采购支出</t>
   </si>
   <si>
@@ -113,21 +112,51 @@
     <t xml:space="preserve">            其中：（1）食材耗用</t>
   </si>
   <si>
+    <t>酒店比上年同期减少餐饮食材采购18万元</t>
+  </si>
+  <si>
+    <t>减少食品的消耗</t>
+  </si>
+  <si>
     <t xml:space="preserve">                      （2）物料消耗</t>
   </si>
   <si>
+    <t>酒店比上年同期减少客用品消耗</t>
+  </si>
+  <si>
+    <t>客房收入缺口大，消耗品也少于预期</t>
+  </si>
+  <si>
     <t xml:space="preserve">                      （3）油气管材</t>
   </si>
   <si>
     <t xml:space="preserve">                      （4）其他材料</t>
   </si>
   <si>
+    <t>酒店比上年同期减少商品成本</t>
+  </si>
+  <si>
+    <t>增加的主要是床垫、防毒面罩、应急手电等低值易耗品及销售商品成本</t>
+  </si>
+  <si>
     <t xml:space="preserve">                  2.外购燃料</t>
   </si>
   <si>
+    <t>酒店上年同期1-2月未经营，且本年度气温较往年较低，空调开启时段加长，用气量增加</t>
+  </si>
+  <si>
+    <t>本年度气温较往年较低，空调开启时段加长，用气量增加</t>
+  </si>
+  <si>
     <t xml:space="preserve">                  3.外购动力</t>
   </si>
   <si>
+    <t>酒店上年同期1-2月未经营，动力随经营收入增加能耗，且设备运行效率偏低，能耗率高。同时由于桔子和影音酒店的合作经营加入影响，租户能耗整体增加。</t>
+  </si>
+  <si>
+    <t>收入未达预期带来的能耗减少</t>
+  </si>
+  <si>
     <t xml:space="preserve">                  4.商旅采购成本</t>
   </si>
   <si>
@@ -137,52 +166,118 @@
     <t xml:space="preserve">        （二）运输费</t>
   </si>
   <si>
+    <t>增加布草调配运输费</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （三）经营性税费</t>
   </si>
   <si>
+    <t>随整体经营收入增加而增加</t>
+  </si>
+  <si>
+    <t>可抵扣进项税增加，增值税及相应附加税减少</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （四）油气分成支出</t>
   </si>
   <si>
     <t xml:space="preserve">        （五）用工薪酬成本</t>
   </si>
   <si>
+    <t>其中上年同期劳务派遣转为外包人工</t>
+  </si>
+  <si>
+    <t>合同化减少1人</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （六）外包劳务支出</t>
   </si>
   <si>
+    <t>其中上年同期劳务派遣转为外包人工，较同期增加餐饮业务外包费用累计40万元，增加销售外包人员共计16万元</t>
+  </si>
+  <si>
+    <t>其中主要是餐饮收入减少带来的餐饮业务外包费用减少</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （七）维修费</t>
   </si>
   <si>
+    <t>增加隐患类整改14万元，大堂、二楼装饰改造工程10.89万元</t>
+  </si>
+  <si>
+    <t>增加隐患类整改14万元，</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （八）租赁费</t>
   </si>
   <si>
     <t xml:space="preserve">        （九）物业采暖费</t>
   </si>
   <si>
+    <t>客房出租率减少，布草洗涤量减少；适当降低团队布草更换频率及布草配置以下降洗涤费用</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （十）绿化环境卫生费</t>
   </si>
   <si>
+    <t>增加四害消杀0.58万元，二次水箱清洗0.69万元</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （十一）五项费用</t>
   </si>
   <si>
+    <t>办公费及差旅费均有所减少</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （十二）财产性税费(房产、土地）</t>
   </si>
   <si>
+    <t>房产税减少，受桔子、影音酒店的从租、从价政策的影响</t>
+  </si>
+  <si>
+    <t>从租、从价政策的影响</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （十三）折旧折耗及摊销</t>
   </si>
   <si>
+    <t>一项长期待摊费用到期，减少待摊费用</t>
+  </si>
+  <si>
+    <t>部分固定资产提足折旧，一项长期待摊费用到期</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （十四）其他固定成本</t>
   </si>
   <si>
+    <t>减少为上年6月暂估的餐饮费用24万元</t>
+  </si>
+  <si>
+    <t>减少财产保险4万元，审计费1.6万元，销售推广费7.7</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （十五）行政性罚款</t>
   </si>
   <si>
     <t xml:space="preserve">        （十六）信用减值损失</t>
   </si>
   <si>
+    <t>随应收账款余额的下降而下降</t>
+  </si>
+  <si>
+    <t>随应收账款余额的上升而上升，需加速应收账款回收</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （十七）存货差额调整</t>
   </si>
   <si>
     <t xml:space="preserve">        （十八）财务费用（收益为“-”）</t>
+  </si>
+  <si>
+    <t>随收入增加而增加各平台手续费</t>
+  </si>
+  <si>
+    <t>收入未达预算，平台手续费也减少</t>
   </si>
   <si>
     <r>
@@ -214,12 +309,18 @@
     <t xml:space="preserve">        （二十一）营业外收支净额（收益为“-”）</t>
   </si>
   <si>
+    <t>地铁影响的补偿7.95万元</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （二十二）投资收益（收益为“-”）</t>
   </si>
   <si>
     <t xml:space="preserve">        （二十三）其他收益（收益为“-”）</t>
   </si>
   <si>
+    <t>招录贫困地区人员享受的增值税减免政策4月截止</t>
+  </si>
+  <si>
     <t xml:space="preserve">        （二十四）其他非经常性损益（收益为“-”）</t>
   </si>
   <si>
@@ -238,111 +339,21 @@
     <t>酒店自2025年2月26日自营，其中存在2个月的停业影响。收入增加153万元，客房收入增加45万元，租赁收入增加112万元，租赁收入增加为桔子和影音酒店的合作经营加入影响。</t>
   </si>
   <si>
-    <t>客房收入减少97万元，主要是团队收入远低于预算；餐饮收入减少109万元，早餐、团队餐、零点餐收入均低于预算；租赁收入减少37万元，其他收入减少5万元</t>
-  </si>
-  <si>
     <t>比上年同期减少餐饮食材采购</t>
   </si>
   <si>
-    <t>减少食品的消耗</t>
-  </si>
-  <si>
     <t>比上年同期减少客用品消耗</t>
   </si>
   <si>
-    <t>客房收入缺口大，消耗品也少于预期</t>
-  </si>
-  <si>
     <t>比上年同期减少商品成本</t>
   </si>
   <si>
-    <t>增加的主要是床垫、防毒面罩、应急手电等低值易耗品及销售商品成本</t>
-  </si>
-  <si>
     <t>上年同期1-2月未经营，且本年度气温较往年较低，空调开启时段加长，用气量增加</t>
   </si>
   <si>
-    <t>本年度气温较往年较低，空调开启时段加长，用气量增加</t>
-  </si>
-  <si>
     <t>上年同期1-2月未经营，动力随经营收入增加能耗，且设备运行效率偏低，能耗率高</t>
   </si>
   <si>
-    <t>收入未达预期带来的能耗减少</t>
-  </si>
-  <si>
-    <t>增加布草调配运输费</t>
-  </si>
-  <si>
-    <t>随整体经营收入增加而增加</t>
-  </si>
-  <si>
-    <t>可抵扣进项税增加，增值税及相应附加税减少</t>
-  </si>
-  <si>
-    <t>其中上年同期劳务派遣转为外包人工</t>
-  </si>
-  <si>
-    <t>合同化减少1人</t>
-  </si>
-  <si>
-    <t>其中上年同期劳务派遣转为外包人工，较同期增加餐饮业务外包费用累计40万元，增加销售外包人员共计16万元</t>
-  </si>
-  <si>
-    <t>其中主要是餐饮收入减少带来的餐饮业务外包费用减少</t>
-  </si>
-  <si>
-    <t>增加隐患类整改14万元，大堂、二楼装饰改造工程10.89万元</t>
-  </si>
-  <si>
-    <t>增加隐患类整改14万元，</t>
-  </si>
-  <si>
-    <t>客房出租率减少，布草洗涤量减少；适当降低团队布草更换频率及布草配置以下降洗涤费用</t>
-  </si>
-  <si>
-    <t>增加四害消杀0.58万元，二次水箱清洗0.69万元</t>
-  </si>
-  <si>
-    <t>办公费及差旅费均有所减少</t>
-  </si>
-  <si>
-    <t>房产税减少，受桔子、影音酒店的从租、从价政策的影响</t>
-  </si>
-  <si>
-    <t>从租、从价政策的影响</t>
-  </si>
-  <si>
-    <t>一项长期待摊费用到期，减少待摊费用</t>
-  </si>
-  <si>
-    <t>部分固定资产提足折旧，一项长期待摊费用到期</t>
-  </si>
-  <si>
-    <t>减少为上年6月暂估的餐饮费用24万元</t>
-  </si>
-  <si>
-    <t>减少财产保险4万元，审计费1.6万元，销售推广费7.7</t>
-  </si>
-  <si>
-    <t>随应收账款余额的下降而下降</t>
-  </si>
-  <si>
-    <t>随应收账款余额的上升而上升，需加速应收账款回收</t>
-  </si>
-  <si>
-    <t>随收入增加而增加各平台手续费</t>
-  </si>
-  <si>
-    <t>收入未达预算，平台手续费也减少</t>
-  </si>
-  <si>
-    <t>地铁影响的补偿7.95万元</t>
-  </si>
-  <si>
-    <t>招录贫困地区人员享受的增值税减免政策4月截止</t>
-  </si>
-  <si>
     <t>江苏常州酒店能源转售预算执行分析（2026年07月）</t>
   </si>
   <si>
@@ -359,15 +370,6 @@
   </si>
   <si>
     <t>常州酒店项目部销售费用预算执行分析（2026年07月）</t>
-  </si>
-  <si>
-    <t>南京中石油三江口汇能码头物业项目预算执行分析（2026年07月）</t>
-  </si>
-  <si>
-    <t>新增项目</t>
-  </si>
-  <si>
-    <t>新增项目，随收入增加对应成本增加</t>
   </si>
 </sst>
 </file>
@@ -377,7 +379,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00;-#,##0.00;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -466,13 +468,6 @@
       <sz val="14"/>
       <name val="方正仿宋_GBK"/>
     </font>
-    <font>
-      <charset val="134"/>
-      <color theme="1"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="宋体"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -534,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -599,12 +594,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -872,8 +861,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="2" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -946,19 +935,6 @@
       <c r="C7" s="5" t="str">
         <f>HYPERLINK("#'常州酒店项目部销售费用'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5" t="str">
-        <f>HYPERLINK("#'南京中石油三江口汇能码头物业项目'!A1","点击跳转 ➔")</f>
-        <v>点击跳转 ➔</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +961,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1003,60 +979,64 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="9" t="s">
+    </row>
+    <row r="3" ht="150" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>23</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>25</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -1099,7 +1079,7 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>28</v>
       </c>
@@ -1108,27 +1088,35 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
+      <c r="G6" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
+      <c r="I6" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
+      <c r="G7" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
+      <c r="I7" s="12" t="s">
+        <v>33</v>
+      </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -1137,7 +1125,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1153,54 +1141,66 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
+      <c r="G9" s="12" t="s">
+        <v>36</v>
+      </c>
       <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
+      <c r="I9" s="12" t="s">
+        <v>37</v>
+      </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
+      <c r="I10" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="150" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
+      <c r="G11" s="12" t="s">
+        <v>42</v>
+      </c>
       <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
+      <c r="I11" s="12" t="s">
+        <v>43</v>
+      </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1245,34 +1245,42 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
+      <c r="G14" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
+      <c r="I14" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
+      <c r="G15" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
+      <c r="I15" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -1281,7 +1289,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -1297,54 +1305,66 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="112.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>56</v>
+      </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
+      <c r="G19" s="12" t="s">
+        <v>59</v>
+      </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
+      <c r="I19" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
@@ -1353,7 +1373,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -1369,9 +1389,9 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1380,23 +1400,27 @@
       <c r="F21" s="11"/>
       <c r="G21" s="12"/>
       <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
+      <c r="I21" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="H22" s="11"/>
       <c r="I22" s="12"/>
       <c r="J22" s="11"/>
@@ -1405,72 +1429,88 @@
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
+      <c r="I23" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
+      <c r="G24" s="12" t="s">
+        <v>69</v>
+      </c>
       <c r="H24" s="11"/>
-      <c r="I24" s="12"/>
+      <c r="I24" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
+      <c r="G25" s="12" t="s">
+        <v>72</v>
+      </c>
       <c r="H25" s="11"/>
-      <c r="I25" s="12"/>
+      <c r="I25" s="12" t="s">
+        <v>73</v>
+      </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>75</v>
+      </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="12" t="s">
+        <v>76</v>
+      </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -1479,7 +1519,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -1495,18 +1535,22 @@
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="12" t="s">
+        <v>79</v>
+      </c>
       <c r="H28" s="11"/>
-      <c r="I28" s="12"/>
+      <c r="I28" s="12" t="s">
+        <v>80</v>
+      </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
@@ -1515,7 +1559,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -1531,18 +1575,22 @@
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="12"/>
+      <c r="G30" s="12" t="s">
+        <v>83</v>
+      </c>
       <c r="H30" s="11"/>
-      <c r="I30" s="12"/>
+      <c r="I30" s="12" t="s">
+        <v>84</v>
+      </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
@@ -1551,7 +1599,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -1569,7 +1617,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1587,7 +1635,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -1603,18 +1651,22 @@
       <c r="M33" s="11"/>
       <c r="N33" s="11"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="12"/>
+      <c r="G34" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="H34" s="11"/>
-      <c r="I34" s="12"/>
+      <c r="I34" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
@@ -1623,7 +1675,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -1639,18 +1691,22 @@
       <c r="M35" s="11"/>
       <c r="N35" s="11"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="12"/>
+      <c r="G36" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="H36" s="11"/>
-      <c r="I36" s="12"/>
+      <c r="I36" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
@@ -1659,7 +1715,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -1677,7 +1733,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -1695,7 +1751,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -1713,7 +1769,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -1742,15 +1798,15 @@
   <cols>
     <col min="1" max="1" width="53" style="6" customWidth="1"/>
     <col min="2" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="39.375" customWidth="1"/>
+    <col min="7" max="7" width="24.3333333333333" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="31.25" customWidth="1"/>
+    <col min="9" max="9" width="24.3333333333333" customWidth="1"/>
     <col min="10" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1768,69 +1824,69 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="9" t="s">
+    </row>
+    <row r="3" ht="168.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" ht="112.5" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -1868,7 +1924,7 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>28</v>
       </c>
@@ -1878,11 +1934,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -1892,7 +1948,7 @@
     </row>
     <row r="7" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1900,11 +1956,11 @@
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="12" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="12" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
@@ -1914,7 +1970,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1930,9 +1986,9 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -1940,11 +1996,11 @@
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="12" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="12" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
@@ -1952,53 +2008,53 @@
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" ht="56.25" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+        <v>38</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
       <c r="G10" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="24"/>
+        <v>102</v>
+      </c>
+      <c r="H10" s="11"/>
       <c r="I10" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-    </row>
-    <row r="11" ht="56.25" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+    </row>
+    <row r="11" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
+        <v>41</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
       <c r="G11" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="24"/>
+        <v>103</v>
+      </c>
+      <c r="H11" s="11"/>
       <c r="I11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
+        <v>43</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -2016,7 +2072,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -2034,7 +2090,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2042,11 +2098,11 @@
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="12" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="12" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
@@ -2054,9 +2110,9 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -2064,11 +2120,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -2078,7 +2134,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -2094,9 +2150,9 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -2104,11 +2160,11 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -2116,53 +2172,53 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" ht="75" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="112.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
+        <v>55</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H18" s="24"/>
+        <v>56</v>
+      </c>
+      <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-    </row>
-    <row r="19" ht="37.5" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+    </row>
+    <row r="19" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
+        <v>58</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" s="24"/>
+        <v>59</v>
+      </c>
+      <c r="H19" s="11"/>
       <c r="I19" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
+        <v>60</v>
+      </c>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2178,49 +2234,49 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
     </row>
-    <row r="21" ht="75" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
+        <v>62</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="12"/>
-      <c r="H21" s="24"/>
+      <c r="H21" s="11"/>
       <c r="I21" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-    </row>
-    <row r="22" ht="37.5" customHeight="1" spans="1:14" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
+        <v>64</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="H22" s="24"/>
+        <v>65</v>
+      </c>
+      <c r="H22" s="11"/>
       <c r="I22" s="12"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2228,11 +2284,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -2240,9 +2296,9 @@
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
     </row>
-    <row r="24" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2250,11 +2306,11 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -2262,9 +2318,9 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
     </row>
-    <row r="25" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -2272,11 +2328,11 @@
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="12" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -2284,9 +2340,9 @@
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
     </row>
-    <row r="26" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2294,11 +2350,11 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -2308,7 +2364,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2324,9 +2380,9 @@
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
     </row>
-    <row r="28" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2334,11 +2390,11 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="12" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -2348,7 +2404,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -2366,7 +2422,7 @@
     </row>
     <row r="30" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -2374,11 +2430,11 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="12" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -2388,7 +2444,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -2406,7 +2462,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -2424,7 +2480,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -2440,9 +2496,9 @@
       <c r="M33" s="11"/>
       <c r="N33" s="11"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -2450,11 +2506,11 @@
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="12" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="12" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -2464,7 +2520,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -2480,9 +2536,9 @@
       <c r="M35" s="11"/>
       <c r="N35" s="11"/>
     </row>
-    <row r="36" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -2490,11 +2546,11 @@
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="12" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H36" s="11"/>
       <c r="I36" s="12" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
@@ -2504,7 +2560,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -2522,7 +2578,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -2540,7 +2596,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -2558,7 +2614,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -2595,7 +2651,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2613,51 +2669,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -2665,11 +2721,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -2733,7 +2789,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -2751,7 +2807,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -2769,7 +2825,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -2787,7 +2843,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -2805,7 +2861,7 @@
     </row>
     <row r="11" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -2813,11 +2869,11 @@
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="12" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="12" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
@@ -2827,7 +2883,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -2845,7 +2901,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -2863,7 +2919,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2881,7 +2937,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -2899,7 +2955,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -2917,7 +2973,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -2935,7 +2991,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -2953,7 +3009,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -2971,7 +3027,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2989,7 +3045,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3007,7 +3063,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3025,7 +3081,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3043,7 +3099,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3061,7 +3117,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -3079,7 +3135,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3097,7 +3153,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3115,7 +3171,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3133,7 +3189,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3151,7 +3207,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3169,7 +3225,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3187,7 +3243,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3205,7 +3261,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3223,7 +3279,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -3241,7 +3297,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -3259,7 +3315,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -3277,7 +3333,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3295,7 +3351,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -3313,7 +3369,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -3331,7 +3387,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -3368,7 +3424,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3386,51 +3442,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -3502,7 +3558,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -3520,7 +3576,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -3538,7 +3594,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -3556,7 +3612,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -3574,7 +3630,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -3592,7 +3648,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -3610,7 +3666,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -3628,7 +3684,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -3646,7 +3702,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3664,7 +3720,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3682,7 +3738,7 @@
     </row>
     <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3690,7 +3746,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -3702,7 +3758,7 @@
     </row>
     <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3710,7 +3766,7 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
@@ -3722,7 +3778,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -3740,7 +3796,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -3758,7 +3814,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3776,7 +3832,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3794,7 +3850,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3812,7 +3868,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3830,7 +3886,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -3848,7 +3904,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3866,7 +3922,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3884,7 +3940,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3902,7 +3958,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3920,7 +3976,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3938,7 +3994,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3956,7 +4012,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3974,7 +4030,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3992,7 +4048,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -4010,7 +4066,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -4028,7 +4084,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4046,7 +4102,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4064,7 +4120,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -4082,7 +4138,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -4100,7 +4156,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4137,7 +4193,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4155,51 +4211,51 @@
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -4271,7 +4327,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -4289,7 +4345,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -4307,7 +4363,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -4325,7 +4381,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -4343,7 +4399,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -4361,7 +4417,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -4379,7 +4435,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -4397,7 +4453,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -4415,7 +4471,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -4433,7 +4489,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -4451,7 +4507,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -4469,7 +4525,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4487,7 +4543,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4505,7 +4561,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4523,7 +4579,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4541,7 +4597,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -4559,7 +4615,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -4577,7 +4633,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -4595,7 +4651,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -4613,7 +4669,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -4631,7 +4687,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -4649,7 +4705,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -4667,7 +4723,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -4685,7 +4741,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -4703,7 +4759,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -4721,7 +4777,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -4739,7 +4795,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -4757,7 +4813,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -4775,7 +4831,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -4793,7 +4849,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4811,7 +4867,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4829,7 +4885,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -4847,7 +4903,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -4865,7 +4921,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4885,773 +4941,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="53" style="6" customWidth="1"/>
-    <col min="2" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="24.3333333333333" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="24.3333333333333" customWidth="1"/>
-    <col min="10" max="14" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-    </row>
-    <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
 </file>